--- a/asset/data/dns_log.xlsx
+++ b/asset/data/dns_log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13660"/>
+    <workbookView windowWidth="28800" windowHeight="11600"/>
   </bookViews>
   <sheets>
     <sheet name="DNS解析日志" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <t>导出账号:zoudaxiong（管理员）</t>
   </si>
   <si>
-    <t>导出范围:DNS解析日志 (全部AP节点: ljs_5G / ljs_Guest)</t>
+    <t>导出范围:DNS解析日志 (全部AP节点: LJS_5G / LJS_Guest)</t>
   </si>
   <si>
     <t>时间</t>
@@ -2408,7 +2408,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -2420,12 +2420,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5092,102 +5086,102 @@
       </c>
     </row>
     <row r="118" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A118" s="9" t="s">
+      <c r="A118" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B118" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C118" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E118" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" s="10" t="s">
+      <c r="E118" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="119" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A119" s="9" t="s">
+      <c r="A119" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B119" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C119" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E119" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F119" s="10" t="s">
+      <c r="E119" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="120" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A120" s="9" t="s">
+      <c r="A120" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E120" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" s="10" t="s">
+      <c r="E120" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F121" s="12" t="s">
+      <c r="F121" s="10" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="122" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A122" s="9" t="s">
+      <c r="A122" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E122" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="10" t="s">
+      <c r="E122" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5212,62 +5206,62 @@
       </c>
     </row>
     <row r="124" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A124" s="9" t="s">
+      <c r="A124" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E124" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="10" t="s">
+      <c r="E124" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A125" s="9" t="s">
+      <c r="A125" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B125" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C125" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E125" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="10" t="s">
+      <c r="E125" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A126" s="9" t="s">
+      <c r="A126" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B126" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C126" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E126" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="10" t="s">
+      <c r="E126" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5312,42 +5306,42 @@
       </c>
     </row>
     <row r="129" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A129" s="9" t="s">
+      <c r="A129" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B129" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C129" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="D129" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E129" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" s="10" t="s">
+      <c r="E129" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A130" s="9" t="s">
+      <c r="A130" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B130" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C130" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E130" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" s="10" t="s">
+      <c r="E130" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5372,122 +5366,122 @@
       </c>
     </row>
     <row r="132" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A132" s="9" t="s">
+      <c r="A132" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B132" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C132" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E132" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" s="10" t="s">
+      <c r="E132" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="133" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A133" s="9" t="s">
+      <c r="A133" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B133" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C133" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F133" s="10" t="s">
+      <c r="E133" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="134" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A134" s="9" t="s">
+      <c r="A134" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="D134" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E134" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="10" t="s">
+      <c r="E134" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="135" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C135" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E135" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F135" s="12" t="s">
+      <c r="F135" s="10" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="136" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B136" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C136" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E136" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" s="10" t="s">
+      <c r="E136" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A137" s="9" t="s">
+      <c r="A137" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B137" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C137" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D137" s="10" t="s">
+      <c r="D137" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E137" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="10" t="s">
+      <c r="E137" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5512,42 +5506,42 @@
       </c>
     </row>
     <row r="139" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B139" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C139" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="D139" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E139" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F139" s="10" t="s">
+      <c r="E139" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B140" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C140" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D140" s="10" t="s">
+      <c r="D140" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E140" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" s="10" t="s">
+      <c r="E140" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5572,222 +5566,222 @@
       </c>
     </row>
     <row r="142" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A142" s="9" t="s">
+      <c r="A142" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B142" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C142" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D142" s="10" t="s">
+      <c r="D142" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E142" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" s="10" t="s">
+      <c r="E142" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="143" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B143" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C143" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="D143" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E143" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143" s="10" t="s">
+      <c r="E143" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="144" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A144" s="9" t="s">
+      <c r="A144" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E144" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" s="10" t="s">
+      <c r="E144" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="145" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A145" s="9" t="s">
+      <c r="A145" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B145" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="D145" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E145" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" s="10" t="s">
+      <c r="E145" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="146" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A146" s="9" t="s">
+      <c r="A146" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B146" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C146" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="D146" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E146" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="10" t="s">
+      <c r="E146" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="147" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A147" s="9" t="s">
+      <c r="A147" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B147" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C147" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="D147" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E147" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="10" t="s">
+      <c r="E147" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="148" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A148" s="9" t="s">
+      <c r="A148" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B148" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C148" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="D148" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E148" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="10" t="s">
+      <c r="E148" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="149" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A149" s="9" t="s">
+      <c r="A149" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B149" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C149" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="D149" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E149" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F149" s="10" t="s">
+      <c r="E149" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="150" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A150" s="9" t="s">
+      <c r="A150" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B150" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C150" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D150" s="10" t="s">
+      <c r="D150" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E150" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" s="10" t="s">
+      <c r="E150" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="151" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A151" s="9" t="s">
+      <c r="A151" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B151" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C151" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="D151" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E151" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="10" t="s">
+      <c r="E151" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A152" s="9" t="s">
+      <c r="A152" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B152" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C152" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D152" s="10" t="s">
+      <c r="D152" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E152" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="10" t="s">
+      <c r="E152" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5812,62 +5806,62 @@
       </c>
     </row>
     <row r="154" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A154" s="9" t="s">
+      <c r="A154" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B154" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D154" s="10" t="s">
+      <c r="D154" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E154" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F154" s="10" t="s">
+      <c r="E154" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B155" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C155" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D155" s="10" t="s">
+      <c r="D155" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E155" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F155" s="10" t="s">
+      <c r="E155" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="B156" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C156" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E156" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" s="10" t="s">
+      <c r="E156" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5912,42 +5906,42 @@
       </c>
     </row>
     <row r="159" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A159" s="9" t="s">
+      <c r="A159" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B159" s="10" t="s">
+      <c r="B159" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C159" s="10" t="s">
+      <c r="C159" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D159" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E159" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F159" s="10" t="s">
+      <c r="E159" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A160" s="9" t="s">
+      <c r="A160" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B160" s="10" t="s">
+      <c r="B160" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C160" s="10" t="s">
+      <c r="C160" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D160" s="10" t="s">
+      <c r="D160" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E160" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F160" s="10" t="s">
+      <c r="E160" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5972,122 +5966,122 @@
       </c>
     </row>
     <row r="162" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A162" s="9" t="s">
+      <c r="A162" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B162" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C162" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D162" s="10" t="s">
+      <c r="D162" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E162" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162" s="10" t="s">
+      <c r="E162" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="163" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A163" s="9" t="s">
+      <c r="A163" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D163" s="10" t="s">
+      <c r="D163" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E163" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F163" s="10" t="s">
+      <c r="E163" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="164" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A164" s="9" t="s">
+      <c r="A164" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B164" s="10" t="s">
+      <c r="B164" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D164" s="10" t="s">
+      <c r="D164" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E164" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" s="10" t="s">
+      <c r="E164" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="165" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A165" s="9" t="s">
+      <c r="A165" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B165" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C165" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D165" s="10" t="s">
+      <c r="D165" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E165" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="10" t="s">
+      <c r="E165" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="166" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A166" s="9" t="s">
+      <c r="A166" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B166" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C166" s="10" t="s">
+      <c r="C166" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D166" s="10" t="s">
+      <c r="D166" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E166" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F166" s="10" t="s">
+      <c r="E166" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="167" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A167" s="9" t="s">
+      <c r="A167" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B167" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C167" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D167" s="10" t="s">
+      <c r="D167" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E167" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F167" s="10" t="s">
+      <c r="E167" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6112,42 +6106,42 @@
       </c>
     </row>
     <row r="169" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A169" s="9" t="s">
+      <c r="A169" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B169" s="10" t="s">
+      <c r="B169" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C169" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D169" s="10" t="s">
+      <c r="D169" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E169" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F169" s="10" t="s">
+      <c r="E169" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F169" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="170" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A170" s="9" t="s">
+      <c r="A170" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B170" s="10" t="s">
+      <c r="B170" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C170" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D170" s="10" t="s">
+      <c r="D170" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E170" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F170" s="10" t="s">
+      <c r="E170" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6172,82 +6166,82 @@
       </c>
     </row>
     <row r="172" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A172" s="9" t="s">
+      <c r="A172" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B172" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C172" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D172" s="10" t="s">
+      <c r="D172" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E172" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F172" s="10" t="s">
+      <c r="E172" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A173" s="9" t="s">
+      <c r="A173" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B173" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C173" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D173" s="10" t="s">
+      <c r="D173" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E173" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="10" t="s">
+      <c r="E173" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A174" s="9" t="s">
+      <c r="A174" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B174" s="10" t="s">
+      <c r="B174" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C174" s="10" t="s">
+      <c r="C174" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E174" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" s="10" t="s">
+      <c r="E174" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="175" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A175" s="9" t="s">
+      <c r="A175" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B175" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C175" s="10" t="s">
+      <c r="C175" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="D175" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E175" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="10" t="s">
+      <c r="E175" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6272,42 +6266,42 @@
       </c>
     </row>
     <row r="177" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A177" s="9" t="s">
+      <c r="A177" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B177" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C177" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D177" s="10" t="s">
+      <c r="D177" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E177" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="10" t="s">
+      <c r="E177" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A178" s="9" t="s">
+      <c r="A178" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B178" s="10" t="s">
+      <c r="B178" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C178" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D178" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E178" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F178" s="10" t="s">
+      <c r="E178" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6332,142 +6326,142 @@
       </c>
     </row>
     <row r="180" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A180" s="9" t="s">
+      <c r="A180" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B180" s="10" t="s">
+      <c r="B180" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C180" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D180" s="10" t="s">
+      <c r="D180" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E180" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="10" t="s">
+      <c r="E180" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="181" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A181" s="9" t="s">
+      <c r="A181" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B181" s="10" t="s">
+      <c r="B181" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C181" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D181" s="10" t="s">
+      <c r="D181" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E181" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F181" s="10" t="s">
+      <c r="E181" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F181" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="182" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A182" s="9" t="s">
+      <c r="A182" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="B182" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C182" s="10" t="s">
+      <c r="C182" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D182" s="10" t="s">
+      <c r="D182" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E182" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="10" t="s">
+      <c r="E182" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="183" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A183" s="9" t="s">
+      <c r="A183" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B183" s="10" t="s">
+      <c r="B183" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C183" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D183" s="10" t="s">
+      <c r="D183" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E183" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F183" s="10" t="s">
+      <c r="E183" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="184" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A184" s="9" t="s">
+      <c r="A184" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B184" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C184" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D184" s="10" t="s">
+      <c r="D184" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E184" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F184" s="10" t="s">
+      <c r="E184" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="185" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A185" s="9" t="s">
+      <c r="A185" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B185" s="10" t="s">
+      <c r="B185" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C185" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="D185" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E185" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F185" s="10" t="s">
+      <c r="E185" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="186" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A186" s="9" t="s">
+      <c r="A186" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B186" s="10" t="s">
+      <c r="B186" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C186" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D186" s="10" t="s">
+      <c r="D186" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E186" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F186" s="10" t="s">
+      <c r="E186" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6492,42 +6486,42 @@
       </c>
     </row>
     <row r="188" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A188" s="9" t="s">
+      <c r="A188" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B188" s="10" t="s">
+      <c r="B188" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="D188" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E188" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="10" t="s">
+      <c r="E188" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="189" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A189" s="9" t="s">
+      <c r="A189" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B189" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C189" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D189" s="10" t="s">
+      <c r="D189" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E189" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F189" s="10" t="s">
+      <c r="E189" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F189" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6552,122 +6546,122 @@
       </c>
     </row>
     <row r="191" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A191" s="9" t="s">
+      <c r="A191" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B191" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="C191" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D191" s="10" t="s">
+      <c r="D191" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E191" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F191" s="10" t="s">
+      <c r="E191" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F191" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A192" s="9" t="s">
+      <c r="A192" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C192" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D192" s="10" t="s">
+      <c r="D192" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E192" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F192" s="10" t="s">
+      <c r="E192" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F192" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A193" s="9" t="s">
+      <c r="A193" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B193" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C193" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D193" s="10" t="s">
+      <c r="D193" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E193" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F193" s="10" t="s">
+      <c r="E193" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F193" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A194" s="9" t="s">
+      <c r="A194" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B194" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C194" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D194" s="10" t="s">
+      <c r="D194" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E194" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F194" s="10" t="s">
+      <c r="E194" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A195" s="9" t="s">
+      <c r="A195" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B195" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C195" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D195" s="10" t="s">
+      <c r="D195" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E195" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F195" s="10" t="s">
+      <c r="E195" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A196" s="9" t="s">
+      <c r="A196" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B196" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C196" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D196" s="10" t="s">
+      <c r="D196" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E196" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="10" t="s">
+      <c r="E196" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6692,102 +6686,102 @@
       </c>
     </row>
     <row r="198" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A198" s="9" t="s">
+      <c r="A198" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B198" s="10" t="s">
+      <c r="B198" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C198" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D198" s="10" t="s">
+      <c r="D198" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E198" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F198" s="10" t="s">
+      <c r="E198" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A199" s="9" t="s">
+      <c r="A199" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="B199" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D199" s="10" t="s">
+      <c r="D199" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E199" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F199" s="10" t="s">
+      <c r="E199" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A200" s="9" t="s">
+      <c r="A200" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B200" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C200" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D200" s="10" t="s">
+      <c r="D200" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E200" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F200" s="10" t="s">
+      <c r="E200" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F200" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="201" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A201" s="9" t="s">
+      <c r="A201" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B201" s="10" t="s">
+      <c r="B201" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C201" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="D201" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E201" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F201" s="10" t="s">
+      <c r="E201" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A202" s="9" t="s">
+      <c r="A202" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B202" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C202" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="D202" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F202" s="10" t="s">
+      <c r="E202" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6812,42 +6806,42 @@
       </c>
     </row>
     <row r="204" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A204" s="9" t="s">
+      <c r="A204" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B204" s="10" t="s">
+      <c r="B204" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C204" s="10" t="s">
+      <c r="C204" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="D204" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E204" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F204" s="10" t="s">
+      <c r="E204" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F204" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A205" s="9" t="s">
+      <c r="A205" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B205" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C205" s="10" t="s">
+      <c r="C205" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="D205" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E205" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F205" s="10" t="s">
+      <c r="E205" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F205" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6872,62 +6866,62 @@
       </c>
     </row>
     <row r="207" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A207" s="9" t="s">
+      <c r="A207" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B207" s="10" t="s">
+      <c r="B207" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C207" s="10" t="s">
+      <c r="C207" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D207" s="10" t="s">
+      <c r="D207" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E207" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F207" s="10" t="s">
+      <c r="E207" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="208" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A208" s="9" t="s">
+      <c r="A208" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B208" s="10" t="s">
+      <c r="B208" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C208" s="10" t="s">
+      <c r="C208" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E208" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="10" t="s">
+      <c r="E208" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F208" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A209" s="9" t="s">
+      <c r="A209" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B209" s="10" t="s">
+      <c r="B209" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C209" s="10" t="s">
+      <c r="C209" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E209" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F209" s="10" t="s">
+      <c r="E209" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F209" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6952,22 +6946,22 @@
       </c>
     </row>
     <row r="211" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A211" s="9" t="s">
+      <c r="A211" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B211" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C211" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E211" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F211" s="10" t="s">
+      <c r="E211" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F211" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6992,22 +6986,22 @@
       </c>
     </row>
     <row r="213" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A213" s="9" t="s">
+      <c r="A213" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B213" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C213" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E213" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F213" s="10" t="s">
+      <c r="E213" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F213" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7072,62 +7066,62 @@
       </c>
     </row>
     <row r="217" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A217" s="9" t="s">
+      <c r="A217" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B217" s="10" t="s">
+      <c r="B217" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C217" s="10" t="s">
+      <c r="C217" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="D217" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E217" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F217" s="10" t="s">
+      <c r="E217" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A218" s="9" t="s">
+      <c r="A218" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B218" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C218" s="10" t="s">
+      <c r="C218" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E218" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F218" s="10" t="s">
+      <c r="E218" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F218" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A219" s="9" t="s">
+      <c r="A219" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B219" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C219" s="10" t="s">
+      <c r="C219" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E219" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F219" s="10" t="s">
+      <c r="E219" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F219" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7152,42 +7146,42 @@
       </c>
     </row>
     <row r="221" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A221" s="9" t="s">
+      <c r="A221" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B221" s="10" t="s">
+      <c r="B221" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C221" s="10" t="s">
+      <c r="C221" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E221" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" s="10" t="s">
+      <c r="E221" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F221" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A222" s="9" t="s">
+      <c r="A222" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B222" s="10" t="s">
+      <c r="B222" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C222" s="10" t="s">
+      <c r="C222" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D222" s="10" t="s">
+      <c r="D222" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E222" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="10" t="s">
+      <c r="E222" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7232,42 +7226,42 @@
       </c>
     </row>
     <row r="225" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A225" s="9" t="s">
+      <c r="A225" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B225" s="10" t="s">
+      <c r="B225" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C225" s="10" t="s">
+      <c r="C225" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E225" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="10" t="s">
+      <c r="E225" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F225" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A226" s="9" t="s">
+      <c r="A226" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B226" s="10" t="s">
+      <c r="B226" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C226" s="10" t="s">
+      <c r="C226" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D226" s="10" t="s">
+      <c r="D226" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E226" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F226" s="10" t="s">
+      <c r="E226" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F226" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7292,22 +7286,22 @@
       </c>
     </row>
     <row r="228" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A228" s="9" t="s">
+      <c r="A228" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B228" s="10" t="s">
+      <c r="B228" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C228" s="10" t="s">
+      <c r="C228" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D228" s="10" t="s">
+      <c r="D228" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E228" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F228" s="10" t="s">
+      <c r="E228" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7352,22 +7346,22 @@
       </c>
     </row>
     <row r="231" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A231" s="9" t="s">
+      <c r="A231" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B231" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C231" s="10" t="s">
+      <c r="C231" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D231" s="10" t="s">
+      <c r="D231" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E231" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F231" s="10" t="s">
+      <c r="E231" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F231" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7392,22 +7386,22 @@
       </c>
     </row>
     <row r="233" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A233" s="9" t="s">
+      <c r="A233" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B233" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C233" s="10" t="s">
+      <c r="C233" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D233" s="10" t="s">
+      <c r="D233" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E233" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F233" s="10" t="s">
+      <c r="E233" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7432,362 +7426,362 @@
       </c>
     </row>
     <row r="235" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A235" s="9" t="s">
+      <c r="A235" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B235" s="10" t="s">
+      <c r="B235" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C235" s="10" t="s">
+      <c r="C235" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D235" s="10" t="s">
+      <c r="D235" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E235" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="10" t="s">
+      <c r="E235" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="236" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A236" s="9" t="s">
+      <c r="A236" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B236" s="10" t="s">
+      <c r="B236" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C236" s="10" t="s">
+      <c r="C236" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="D236" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E236" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F236" s="10" t="s">
+      <c r="E236" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F236" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A237" s="9" t="s">
+      <c r="A237" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B237" s="10" t="s">
+      <c r="B237" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C237" s="10" t="s">
+      <c r="C237" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="D237" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E237" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F237" s="10" t="s">
+      <c r="E237" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F237" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="238" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A238" s="9" t="s">
+      <c r="A238" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B238" s="10" t="s">
+      <c r="B238" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C238" s="10" t="s">
+      <c r="C238" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E238" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F238" s="10" t="s">
+      <c r="E238" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="239" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A239" s="9" t="s">
+      <c r="A239" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B239" s="10" t="s">
+      <c r="B239" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="C239" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E239" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F239" s="10" t="s">
+      <c r="E239" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F239" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="240" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A240" s="9" t="s">
+      <c r="A240" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="B240" s="10" t="s">
+      <c r="B240" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C240" s="10" t="s">
+      <c r="C240" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E240" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F240" s="10" t="s">
+      <c r="E240" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="241" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A241" s="9" t="s">
+      <c r="A241" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B241" s="10" t="s">
+      <c r="B241" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C241" s="10" t="s">
+      <c r="C241" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D241" s="10" t="s">
+      <c r="D241" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E241" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="10" t="s">
+      <c r="E241" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="242" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A242" s="9" t="s">
+      <c r="A242" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B242" s="10" t="s">
+      <c r="B242" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C242" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D242" s="10" t="s">
+      <c r="D242" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E242" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F242" s="10" t="s">
+      <c r="E242" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F242" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="243" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A243" s="9" t="s">
+      <c r="A243" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B243" s="10" t="s">
+      <c r="B243" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C243" s="10" t="s">
+      <c r="C243" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D243" s="10" t="s">
+      <c r="D243" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E243" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F243" s="10" t="s">
+      <c r="E243" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="244" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A244" s="9" t="s">
+      <c r="A244" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B244" s="10" t="s">
+      <c r="B244" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C244" s="10" t="s">
+      <c r="C244" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D244" s="10" t="s">
+      <c r="D244" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E244" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F244" s="10" t="s">
+      <c r="E244" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="245" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A245" s="9" t="s">
+      <c r="A245" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B245" s="10" t="s">
+      <c r="B245" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C245" s="10" t="s">
+      <c r="C245" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D245" s="10" t="s">
+      <c r="D245" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E245" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F245" s="10" t="s">
+      <c r="E245" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="246" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A246" s="9" t="s">
+      <c r="A246" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B246" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C246" s="10" t="s">
+      <c r="C246" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D246" s="10" t="s">
+      <c r="D246" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E246" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F246" s="10" t="s">
+      <c r="E246" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="247" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A247" s="9" t="s">
+      <c r="A247" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B247" s="10" t="s">
+      <c r="B247" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C247" s="10" t="s">
+      <c r="C247" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D247" s="10" t="s">
+      <c r="D247" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E247" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="10" t="s">
+      <c r="E247" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="248" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A248" s="9" t="s">
+      <c r="A248" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B248" s="10" t="s">
+      <c r="B248" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C248" s="10" t="s">
+      <c r="C248" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D248" s="10" t="s">
+      <c r="D248" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E248" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F248" s="10" t="s">
+      <c r="E248" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F248" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="249" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A249" s="9" t="s">
+      <c r="A249" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B249" s="10" t="s">
+      <c r="B249" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C249" s="10" t="s">
+      <c r="C249" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D249" s="10" t="s">
+      <c r="D249" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E249" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F249" s="10" t="s">
+      <c r="E249" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F249" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="250" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A250" s="9" t="s">
+      <c r="A250" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B250" s="10" t="s">
+      <c r="B250" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C250" s="10" t="s">
+      <c r="C250" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="D250" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E250" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F250" s="10" t="s">
+      <c r="E250" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="251" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A251" s="9" t="s">
+      <c r="A251" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B251" s="10" t="s">
+      <c r="B251" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C251" s="10" t="s">
+      <c r="C251" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D251" s="10" t="s">
+      <c r="D251" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E251" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F251" s="10" t="s">
+      <c r="E251" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F251" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="252" s="2" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A252" s="9" t="s">
+      <c r="A252" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B252" s="10" t="s">
+      <c r="B252" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C252" s="10" t="s">
+      <c r="C252" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E252" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F252" s="10" t="s">
+      <c r="E252" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F252" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8292,22 +8286,22 @@
       </c>
     </row>
     <row r="278" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A278" s="9" t="s">
+      <c r="A278" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B278" s="10" t="s">
+      <c r="B278" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C278" s="10" t="s">
+      <c r="C278" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D278" s="10" t="s">
+      <c r="D278" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E278" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F278" s="10" t="s">
+      <c r="E278" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F278" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8332,282 +8326,282 @@
       </c>
     </row>
     <row r="280" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A280" s="9" t="s">
+      <c r="A280" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B280" s="10" t="s">
+      <c r="B280" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C280" s="10" t="s">
+      <c r="C280" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D280" s="10" t="s">
+      <c r="D280" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E280" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F280" s="10" t="s">
+      <c r="E280" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F280" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="281" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A281" s="9" t="s">
+      <c r="A281" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B281" s="10" t="s">
+      <c r="B281" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C281" s="10" t="s">
+      <c r="C281" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="D281" s="10" t="s">
+      <c r="D281" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E281" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F281" s="10" t="s">
+      <c r="E281" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F281" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="282" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A282" s="9" t="s">
+      <c r="A282" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B282" s="10" t="s">
+      <c r="B282" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C282" s="10" t="s">
+      <c r="C282" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D282" s="10" t="s">
+      <c r="D282" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E282" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F282" s="10" t="s">
+      <c r="E282" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F282" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="283" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A283" s="9" t="s">
+      <c r="A283" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B283" s="10" t="s">
+      <c r="B283" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C283" s="10" t="s">
+      <c r="C283" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D283" s="10" t="s">
+      <c r="D283" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E283" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F283" s="10" t="s">
+      <c r="E283" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F283" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="284" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A284" s="9" t="s">
+      <c r="A284" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B284" s="10" t="s">
+      <c r="B284" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C284" s="10" t="s">
+      <c r="C284" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D284" s="10" t="s">
+      <c r="D284" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E284" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F284" s="10" t="s">
+      <c r="E284" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F284" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="285" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A285" s="9" t="s">
+      <c r="A285" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B285" s="10" t="s">
+      <c r="B285" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C285" s="10" t="s">
+      <c r="C285" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="D285" s="10" t="s">
+      <c r="D285" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E285" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F285" s="10" t="s">
+      <c r="E285" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F285" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="286" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A286" s="9" t="s">
+      <c r="A286" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B286" s="10" t="s">
+      <c r="B286" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C286" s="10" t="s">
+      <c r="C286" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D286" s="10" t="s">
+      <c r="D286" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E286" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="10" t="s">
+      <c r="E286" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F286" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="287" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A287" s="9" t="s">
+      <c r="A287" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="B287" s="10" t="s">
+      <c r="B287" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C287" s="10" t="s">
+      <c r="C287" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D287" s="10" t="s">
+      <c r="D287" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E287" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F287" s="10" t="s">
+      <c r="E287" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F287" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="288" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A288" s="9" t="s">
+      <c r="A288" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B288" s="10" t="s">
+      <c r="B288" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C288" s="10" t="s">
+      <c r="C288" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="D288" s="10" t="s">
+      <c r="D288" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E288" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F288" s="10" t="s">
+      <c r="E288" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F288" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="289" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A289" s="9" t="s">
+      <c r="A289" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B289" s="10" t="s">
+      <c r="B289" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C289" s="10" t="s">
+      <c r="C289" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D289" s="10" t="s">
+      <c r="D289" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E289" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F289" s="10" t="s">
+      <c r="E289" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F289" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="290" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A290" s="9" t="s">
+      <c r="A290" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B290" s="10" t="s">
+      <c r="B290" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C290" s="10" t="s">
+      <c r="C290" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D290" s="10" t="s">
+      <c r="D290" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E290" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F290" s="10" t="s">
+      <c r="E290" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F290" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A291" s="9" t="s">
+      <c r="A291" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B291" s="10" t="s">
+      <c r="B291" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C291" s="10" t="s">
+      <c r="C291" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D291" s="10" t="s">
+      <c r="D291" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E291" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F291" s="10" t="s">
+      <c r="E291" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F291" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="292" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A292" s="9" t="s">
+      <c r="A292" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B292" s="10" t="s">
+      <c r="B292" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C292" s="10" t="s">
+      <c r="C292" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D292" s="10" t="s">
+      <c r="D292" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E292" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F292" s="10" t="s">
+      <c r="E292" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F292" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="293" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A293" s="9" t="s">
+      <c r="A293" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B293" s="10" t="s">
+      <c r="B293" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C293" s="10" t="s">
+      <c r="C293" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="D293" s="10" t="s">
+      <c r="D293" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E293" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F293" s="10" t="s">
+      <c r="E293" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F293" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8652,22 +8646,22 @@
       </c>
     </row>
     <row r="296" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A296" s="9" t="s">
+      <c r="A296" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B296" s="10" t="s">
+      <c r="B296" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C296" s="10" t="s">
+      <c r="C296" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D296" s="10" t="s">
+      <c r="D296" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E296" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F296" s="10" t="s">
+      <c r="E296" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F296" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8712,42 +8706,42 @@
       </c>
     </row>
     <row r="299" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A299" s="9" t="s">
+      <c r="A299" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="B299" s="10" t="s">
+      <c r="B299" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C299" s="10" t="s">
+      <c r="C299" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D299" s="10" t="s">
+      <c r="D299" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E299" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F299" s="10" t="s">
+      <c r="E299" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F299" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A300" s="9" t="s">
+      <c r="A300" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B300" s="10" t="s">
+      <c r="B300" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C300" s="10" t="s">
+      <c r="C300" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D300" s="10" t="s">
+      <c r="D300" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E300" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F300" s="10" t="s">
+      <c r="E300" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F300" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8772,62 +8766,62 @@
       </c>
     </row>
     <row r="302" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A302" s="9" t="s">
+      <c r="A302" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="B302" s="10" t="s">
+      <c r="B302" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C302" s="10" t="s">
+      <c r="C302" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D302" s="10" t="s">
+      <c r="D302" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E302" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F302" s="10" t="s">
+      <c r="E302" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F302" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A303" s="9" t="s">
+      <c r="A303" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B303" s="10" t="s">
+      <c r="B303" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C303" s="10" t="s">
+      <c r="C303" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D303" s="10" t="s">
+      <c r="D303" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E303" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F303" s="10" t="s">
+      <c r="E303" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F303" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="304" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A304" s="9" t="s">
+      <c r="A304" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="B304" s="10" t="s">
+      <c r="B304" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C304" s="10" t="s">
+      <c r="C304" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D304" s="10" t="s">
+      <c r="D304" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E304" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F304" s="10" t="s">
+      <c r="E304" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F304" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8852,82 +8846,82 @@
       </c>
     </row>
     <row r="306" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A306" s="9" t="s">
+      <c r="A306" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="B306" s="10" t="s">
+      <c r="B306" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C306" s="10" t="s">
+      <c r="C306" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D306" s="10" t="s">
+      <c r="D306" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E306" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F306" s="10" t="s">
+      <c r="E306" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F306" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A307" s="9" t="s">
+      <c r="A307" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B307" s="10" t="s">
+      <c r="B307" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C307" s="10" t="s">
+      <c r="C307" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D307" s="10" t="s">
+      <c r="D307" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E307" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F307" s="10" t="s">
+      <c r="E307" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F307" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A308" s="9" t="s">
+      <c r="A308" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="B308" s="10" t="s">
+      <c r="B308" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C308" s="10" t="s">
+      <c r="C308" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D308" s="10" t="s">
+      <c r="D308" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E308" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F308" s="10" t="s">
+      <c r="E308" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="309" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A309" s="9" t="s">
+      <c r="A309" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="B309" s="10" t="s">
+      <c r="B309" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C309" s="10" t="s">
+      <c r="C309" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D309" s="10" t="s">
+      <c r="D309" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E309" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F309" s="10" t="s">
+      <c r="E309" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F309" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9032,22 +9026,22 @@
       </c>
     </row>
     <row r="315" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A315" s="9" t="s">
+      <c r="A315" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B315" s="10" t="s">
+      <c r="B315" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C315" s="10" t="s">
+      <c r="C315" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E315" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F315" s="10" t="s">
+      <c r="E315" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F315" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9072,62 +9066,62 @@
       </c>
     </row>
     <row r="317" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A317" s="9" t="s">
+      <c r="A317" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B317" s="10" t="s">
+      <c r="B317" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C317" s="10" t="s">
+      <c r="C317" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D317" s="10" t="s">
+      <c r="D317" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E317" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F317" s="10" t="s">
+      <c r="E317" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F317" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="318" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A318" s="9" t="s">
+      <c r="A318" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B318" s="10" t="s">
+      <c r="B318" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C318" s="10" t="s">
+      <c r="C318" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D318" s="10" t="s">
+      <c r="D318" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E318" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F318" s="10" t="s">
+      <c r="E318" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="319" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A319" s="9" t="s">
+      <c r="A319" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B319" s="10" t="s">
+      <c r="B319" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C319" s="10" t="s">
+      <c r="C319" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D319" s="10" t="s">
+      <c r="D319" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E319" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F319" s="10" t="s">
+      <c r="E319" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F319" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9152,42 +9146,42 @@
       </c>
     </row>
     <row r="321" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A321" s="9" t="s">
+      <c r="A321" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B321" s="10" t="s">
+      <c r="B321" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C321" s="10" t="s">
+      <c r="C321" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D321" s="10" t="s">
+      <c r="D321" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E321" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F321" s="10" t="s">
+      <c r="E321" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F321" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A322" s="9" t="s">
+      <c r="A322" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B322" s="10" t="s">
+      <c r="B322" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C322" s="10" t="s">
+      <c r="C322" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D322" s="10" t="s">
+      <c r="D322" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E322" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F322" s="10" t="s">
+      <c r="E322" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F322" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9212,42 +9206,42 @@
       </c>
     </row>
     <row r="324" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A324" s="9" t="s">
+      <c r="A324" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="B324" s="10" t="s">
+      <c r="B324" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C324" s="10" t="s">
+      <c r="C324" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D324" s="10" t="s">
+      <c r="D324" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E324" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F324" s="10" t="s">
+      <c r="E324" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F324" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A325" s="9" t="s">
+      <c r="A325" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="B325" s="10" t="s">
+      <c r="B325" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C325" s="10" t="s">
+      <c r="C325" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D325" s="10" t="s">
+      <c r="D325" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E325" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F325" s="10" t="s">
+      <c r="E325" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F325" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9312,22 +9306,22 @@
       </c>
     </row>
     <row r="329" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A329" s="9" t="s">
+      <c r="A329" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B329" s="10" t="s">
+      <c r="B329" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C329" s="10" t="s">
+      <c r="C329" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D329" s="10" t="s">
+      <c r="D329" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E329" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F329" s="10" t="s">
+      <c r="E329" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F329" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9352,122 +9346,122 @@
       </c>
     </row>
     <row r="331" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A331" s="9" t="s">
+      <c r="A331" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B331" s="10" t="s">
+      <c r="B331" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C331" s="10" t="s">
+      <c r="C331" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D331" s="10" t="s">
+      <c r="D331" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E331" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F331" s="10" t="s">
+      <c r="E331" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F331" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A332" s="9" t="s">
+      <c r="A332" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="B332" s="10" t="s">
+      <c r="B332" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C332" s="10" t="s">
+      <c r="C332" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D332" s="10" t="s">
+      <c r="D332" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E332" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F332" s="10" t="s">
+      <c r="E332" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F332" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A333" s="9" t="s">
+      <c r="A333" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="B333" s="10" t="s">
+      <c r="B333" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C333" s="10" t="s">
+      <c r="C333" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D333" s="10" t="s">
+      <c r="D333" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E333" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F333" s="10" t="s">
+      <c r="E333" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F333" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="334" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A334" s="9" t="s">
+      <c r="A334" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B334" s="10" t="s">
+      <c r="B334" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C334" s="10" t="s">
+      <c r="C334" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D334" s="10" t="s">
+      <c r="D334" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E334" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F334" s="10" t="s">
+      <c r="E334" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F334" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A335" s="9" t="s">
+      <c r="A335" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B335" s="10" t="s">
+      <c r="B335" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C335" s="10" t="s">
+      <c r="C335" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D335" s="10" t="s">
+      <c r="D335" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E335" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F335" s="10" t="s">
+      <c r="E335" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F335" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A336" s="9" t="s">
+      <c r="A336" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="B336" s="10" t="s">
+      <c r="B336" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C336" s="10" t="s">
+      <c r="C336" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D336" s="10" t="s">
+      <c r="D336" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E336" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F336" s="10" t="s">
+      <c r="E336" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F336" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9492,62 +9486,62 @@
       </c>
     </row>
     <row r="338" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A338" s="9" t="s">
+      <c r="A338" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B338" s="10" t="s">
+      <c r="B338" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C338" s="10" t="s">
+      <c r="C338" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D338" s="10" t="s">
+      <c r="D338" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E338" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F338" s="10" t="s">
+      <c r="E338" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F338" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A339" s="9" t="s">
+      <c r="A339" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B339" s="10" t="s">
+      <c r="B339" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C339" s="10" t="s">
+      <c r="C339" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D339" s="10" t="s">
+      <c r="D339" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E339" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F339" s="10" t="s">
+      <c r="E339" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F339" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A340" s="9" t="s">
+      <c r="A340" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B340" s="10" t="s">
+      <c r="B340" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C340" s="10" t="s">
+      <c r="C340" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D340" s="10" t="s">
+      <c r="D340" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E340" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F340" s="10" t="s">
+      <c r="E340" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F340" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9692,22 +9686,22 @@
       </c>
     </row>
     <row r="348" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A348" s="9" t="s">
+      <c r="A348" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B348" s="10" t="s">
+      <c r="B348" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C348" s="10" t="s">
+      <c r="C348" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D348" s="10" t="s">
+      <c r="D348" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E348" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F348" s="10" t="s">
+      <c r="E348" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F348" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9732,162 +9726,162 @@
       </c>
     </row>
     <row r="350" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A350" s="9" t="s">
+      <c r="A350" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="B350" s="10" t="s">
+      <c r="B350" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C350" s="10" t="s">
+      <c r="C350" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D350" s="10" t="s">
+      <c r="D350" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E350" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F350" s="10" t="s">
+      <c r="E350" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F350" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A351" s="9" t="s">
+      <c r="A351" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B351" s="10" t="s">
+      <c r="B351" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C351" s="10" t="s">
+      <c r="C351" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D351" s="10" t="s">
+      <c r="D351" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E351" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F351" s="10" t="s">
+      <c r="E351" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F351" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="352" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A352" s="9" t="s">
+      <c r="A352" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="B352" s="10" t="s">
+      <c r="B352" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C352" s="10" t="s">
+      <c r="C352" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D352" s="10" t="s">
+      <c r="D352" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E352" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F352" s="10" t="s">
+      <c r="E352" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A353" s="9" t="s">
+      <c r="A353" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B353" s="10" t="s">
+      <c r="B353" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C353" s="10" t="s">
+      <c r="C353" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D353" s="10" t="s">
+      <c r="D353" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E353" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F353" s="10" t="s">
+      <c r="E353" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F353" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A354" s="9" t="s">
+      <c r="A354" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="B354" s="10" t="s">
+      <c r="B354" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C354" s="10" t="s">
+      <c r="C354" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D354" s="10" t="s">
+      <c r="D354" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E354" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F354" s="10" t="s">
+      <c r="E354" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A355" s="9" t="s">
+      <c r="A355" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B355" s="10" t="s">
+      <c r="B355" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C355" s="10" t="s">
+      <c r="C355" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D355" s="10" t="s">
+      <c r="D355" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E355" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F355" s="10" t="s">
+      <c r="E355" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F355" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="356" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A356" s="9" t="s">
+      <c r="A356" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B356" s="10" t="s">
+      <c r="B356" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C356" s="10" t="s">
+      <c r="C356" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D356" s="10" t="s">
+      <c r="D356" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E356" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F356" s="10" t="s">
+      <c r="E356" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F356" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A357" s="9" t="s">
+      <c r="A357" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B357" s="10" t="s">
+      <c r="B357" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C357" s="10" t="s">
+      <c r="C357" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D357" s="10" t="s">
+      <c r="D357" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E357" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F357" s="10" t="s">
+      <c r="E357" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F357" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9912,62 +9906,62 @@
       </c>
     </row>
     <row r="359" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A359" s="9" t="s">
+      <c r="A359" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B359" s="10" t="s">
+      <c r="B359" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C359" s="10" t="s">
+      <c r="C359" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D359" s="10" t="s">
+      <c r="D359" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E359" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F359" s="10" t="s">
+      <c r="E359" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="360" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A360" s="9" t="s">
+      <c r="A360" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B360" s="10" t="s">
+      <c r="B360" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C360" s="10" t="s">
+      <c r="C360" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D360" s="10" t="s">
+      <c r="D360" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E360" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F360" s="10" t="s">
+      <c r="E360" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F360" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="361" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A361" s="9" t="s">
+      <c r="A361" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="B361" s="10" t="s">
+      <c r="B361" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C361" s="10" t="s">
+      <c r="C361" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D361" s="10" t="s">
+      <c r="D361" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E361" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F361" s="10" t="s">
+      <c r="E361" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F361" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -9992,22 +9986,22 @@
       </c>
     </row>
     <row r="363" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A363" s="9" t="s">
+      <c r="A363" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="B363" s="10" t="s">
+      <c r="B363" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C363" s="10" t="s">
+      <c r="C363" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D363" s="10" t="s">
+      <c r="D363" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E363" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F363" s="10" t="s">
+      <c r="E363" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F363" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10032,82 +10026,82 @@
       </c>
     </row>
     <row r="365" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A365" s="9" t="s">
+      <c r="A365" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B365" s="10" t="s">
+      <c r="B365" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C365" s="10" t="s">
+      <c r="C365" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D365" s="10" t="s">
+      <c r="D365" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E365" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F365" s="10" t="s">
+      <c r="E365" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F365" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="366" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A366" s="9" t="s">
+      <c r="A366" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B366" s="10" t="s">
+      <c r="B366" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C366" s="10" t="s">
+      <c r="C366" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D366" s="10" t="s">
+      <c r="D366" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E366" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F366" s="10" t="s">
+      <c r="E366" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F366" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="367" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A367" s="9" t="s">
+      <c r="A367" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B367" s="10" t="s">
+      <c r="B367" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C367" s="10" t="s">
+      <c r="C367" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D367" s="10" t="s">
+      <c r="D367" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E367" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F367" s="10" t="s">
+      <c r="E367" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F367" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="368" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A368" s="9" t="s">
+      <c r="A368" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="B368" s="10" t="s">
+      <c r="B368" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C368" s="10" t="s">
+      <c r="C368" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D368" s="10" t="s">
+      <c r="D368" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E368" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F368" s="10" t="s">
+      <c r="E368" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F368" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10292,22 +10286,22 @@
       </c>
     </row>
     <row r="378" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A378" s="9" t="s">
+      <c r="A378" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="B378" s="10" t="s">
+      <c r="B378" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C378" s="10" t="s">
+      <c r="C378" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D378" s="10" t="s">
+      <c r="D378" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E378" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F378" s="10" t="s">
+      <c r="E378" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F378" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10352,42 +10346,42 @@
       </c>
     </row>
     <row r="381" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A381" s="9" t="s">
+      <c r="A381" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B381" s="10" t="s">
+      <c r="B381" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C381" s="10" t="s">
+      <c r="C381" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D381" s="10" t="s">
+      <c r="D381" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E381" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F381" s="10" t="s">
+      <c r="E381" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F381" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="382" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A382" s="9" t="s">
+      <c r="A382" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="B382" s="10" t="s">
+      <c r="B382" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C382" s="10" t="s">
+      <c r="C382" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D382" s="10" t="s">
+      <c r="D382" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E382" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F382" s="10" t="s">
+      <c r="E382" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F382" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10412,82 +10406,82 @@
       </c>
     </row>
     <row r="384" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A384" s="9" t="s">
+      <c r="A384" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B384" s="10" t="s">
+      <c r="B384" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C384" s="10" t="s">
+      <c r="C384" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D384" s="10" t="s">
+      <c r="D384" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E384" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F384" s="10" t="s">
+      <c r="E384" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F384" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="385" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A385" s="9" t="s">
+      <c r="A385" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B385" s="10" t="s">
+      <c r="B385" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C385" s="10" t="s">
+      <c r="C385" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D385" s="10" t="s">
+      <c r="D385" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E385" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F385" s="10" t="s">
+      <c r="E385" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F385" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="386" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A386" s="9" t="s">
+      <c r="A386" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="B386" s="10" t="s">
+      <c r="B386" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C386" s="10" t="s">
+      <c r="C386" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D386" s="10" t="s">
+      <c r="D386" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E386" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F386" s="10" t="s">
+      <c r="E386" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F386" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="387" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A387" s="9" t="s">
+      <c r="A387" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B387" s="10" t="s">
+      <c r="B387" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C387" s="10" t="s">
+      <c r="C387" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D387" s="10" t="s">
+      <c r="D387" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E387" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F387" s="10" t="s">
+      <c r="E387" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F387" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10512,62 +10506,62 @@
       </c>
     </row>
     <row r="389" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A389" s="9" t="s">
+      <c r="A389" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B389" s="10" t="s">
+      <c r="B389" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C389" s="10" t="s">
+      <c r="C389" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D389" s="10" t="s">
+      <c r="D389" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E389" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F389" s="10" t="s">
+      <c r="E389" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F389" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="390" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A390" s="9" t="s">
+      <c r="A390" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="B390" s="10" t="s">
+      <c r="B390" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C390" s="10" t="s">
+      <c r="C390" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D390" s="10" t="s">
+      <c r="D390" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E390" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F390" s="10" t="s">
+      <c r="E390" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F390" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="391" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A391" s="9" t="s">
+      <c r="A391" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B391" s="10" t="s">
+      <c r="B391" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C391" s="10" t="s">
+      <c r="C391" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D391" s="10" t="s">
+      <c r="D391" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E391" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F391" s="10" t="s">
+      <c r="E391" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F391" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10652,22 +10646,22 @@
       </c>
     </row>
     <row r="396" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A396" s="9" t="s">
+      <c r="A396" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B396" s="10" t="s">
+      <c r="B396" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C396" s="10" t="s">
+      <c r="C396" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D396" s="10" t="s">
+      <c r="D396" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E396" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F396" s="10" t="s">
+      <c r="E396" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F396" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10692,62 +10686,62 @@
       </c>
     </row>
     <row r="398" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A398" s="9" t="s">
+      <c r="A398" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B398" s="10" t="s">
+      <c r="B398" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C398" s="10" t="s">
+      <c r="C398" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D398" s="10" t="s">
+      <c r="D398" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E398" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F398" s="10" t="s">
+      <c r="E398" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F398" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="399" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A399" s="9" t="s">
+      <c r="A399" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B399" s="10" t="s">
+      <c r="B399" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C399" s="10" t="s">
+      <c r="C399" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D399" s="10" t="s">
+      <c r="D399" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E399" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F399" s="10" t="s">
+      <c r="E399" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F399" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="400" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A400" s="9" t="s">
+      <c r="A400" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B400" s="10" t="s">
+      <c r="B400" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C400" s="10" t="s">
+      <c r="C400" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D400" s="10" t="s">
+      <c r="D400" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E400" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F400" s="10" t="s">
+      <c r="E400" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10812,102 +10806,102 @@
       </c>
     </row>
     <row r="404" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A404" s="9" t="s">
+      <c r="A404" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B404" s="10" t="s">
+      <c r="B404" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C404" s="10" t="s">
+      <c r="C404" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D404" s="10" t="s">
+      <c r="D404" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E404" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F404" s="10" t="s">
+      <c r="E404" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F404" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="405" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A405" s="9" t="s">
+      <c r="A405" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B405" s="10" t="s">
+      <c r="B405" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C405" s="10" t="s">
+      <c r="C405" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D405" s="10" t="s">
+      <c r="D405" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E405" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F405" s="10" t="s">
+      <c r="E405" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F405" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="406" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A406" s="9" t="s">
+      <c r="A406" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B406" s="10" t="s">
+      <c r="B406" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C406" s="10" t="s">
+      <c r="C406" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D406" s="10" t="s">
+      <c r="D406" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E406" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F406" s="10" t="s">
+      <c r="E406" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F406" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="407" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A407" s="9" t="s">
+      <c r="A407" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B407" s="10" t="s">
+      <c r="B407" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C407" s="10" t="s">
+      <c r="C407" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D407" s="10" t="s">
+      <c r="D407" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E407" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F407" s="10" t="s">
+      <c r="E407" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F407" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="408" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A408" s="9" t="s">
+      <c r="A408" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B408" s="10" t="s">
+      <c r="B408" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C408" s="10" t="s">
+      <c r="C408" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D408" s="10" t="s">
+      <c r="D408" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E408" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F408" s="10" t="s">
+      <c r="E408" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F408" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -10932,82 +10926,82 @@
       </c>
     </row>
     <row r="410" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A410" s="9" t="s">
+      <c r="A410" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="B410" s="10" t="s">
+      <c r="B410" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C410" s="10" t="s">
+      <c r="C410" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D410" s="10" t="s">
+      <c r="D410" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E410" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F410" s="10" t="s">
+      <c r="E410" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F410" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A411" s="9" t="s">
+      <c r="A411" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B411" s="10" t="s">
+      <c r="B411" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C411" s="10" t="s">
+      <c r="C411" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D411" s="10" t="s">
+      <c r="D411" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E411" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F411" s="10" t="s">
+      <c r="E411" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F411" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="412" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A412" s="9" t="s">
+      <c r="A412" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="B412" s="10" t="s">
+      <c r="B412" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C412" s="10" t="s">
+      <c r="C412" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D412" s="10" t="s">
+      <c r="D412" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E412" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F412" s="10" t="s">
+      <c r="E412" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F412" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="413" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A413" s="9" t="s">
+      <c r="A413" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B413" s="10" t="s">
+      <c r="B413" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C413" s="10" t="s">
+      <c r="C413" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D413" s="10" t="s">
+      <c r="D413" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E413" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F413" s="10" t="s">
+      <c r="E413" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F413" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11032,22 +11026,22 @@
       </c>
     </row>
     <row r="415" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A415" s="9" t="s">
+      <c r="A415" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B415" s="10" t="s">
+      <c r="B415" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C415" s="10" t="s">
+      <c r="C415" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D415" s="10" t="s">
+      <c r="D415" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E415" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F415" s="10" t="s">
+      <c r="E415" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F415" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11412,22 +11406,22 @@
       </c>
     </row>
     <row r="434" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A434" s="9" t="s">
+      <c r="A434" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="B434" s="10" t="s">
+      <c r="B434" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C434" s="10" t="s">
+      <c r="C434" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D434" s="10" t="s">
+      <c r="D434" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E434" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F434" s="10" t="s">
+      <c r="E434" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F434" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11452,82 +11446,82 @@
       </c>
     </row>
     <row r="436" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A436" s="9" t="s">
+      <c r="A436" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B436" s="10" t="s">
+      <c r="B436" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C436" s="10" t="s">
+      <c r="C436" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D436" s="10" t="s">
+      <c r="D436" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E436" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F436" s="10" t="s">
+      <c r="E436" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F436" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="437" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A437" s="9" t="s">
+      <c r="A437" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="B437" s="10" t="s">
+      <c r="B437" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C437" s="10" t="s">
+      <c r="C437" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D437" s="10" t="s">
+      <c r="D437" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E437" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F437" s="10" t="s">
+      <c r="E437" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F437" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="438" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A438" s="9" t="s">
+      <c r="A438" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B438" s="10" t="s">
+      <c r="B438" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C438" s="10" t="s">
+      <c r="C438" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D438" s="10" t="s">
+      <c r="D438" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E438" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F438" s="10" t="s">
+      <c r="E438" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F438" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="439" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A439" s="9" t="s">
+      <c r="A439" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="B439" s="10" t="s">
+      <c r="B439" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C439" s="10" t="s">
+      <c r="C439" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D439" s="10" t="s">
+      <c r="D439" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E439" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F439" s="10" t="s">
+      <c r="E439" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F439" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11552,42 +11546,42 @@
       </c>
     </row>
     <row r="441" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A441" s="9" t="s">
+      <c r="A441" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="B441" s="10" t="s">
+      <c r="B441" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C441" s="10" t="s">
+      <c r="C441" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D441" s="10" t="s">
+      <c r="D441" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E441" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F441" s="10" t="s">
+      <c r="E441" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F441" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="442" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A442" s="9" t="s">
+      <c r="A442" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="B442" s="10" t="s">
+      <c r="B442" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C442" s="10" t="s">
+      <c r="C442" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D442" s="10" t="s">
+      <c r="D442" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E442" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F442" s="10" t="s">
+      <c r="E442" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F442" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11612,82 +11606,82 @@
       </c>
     </row>
     <row r="444" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A444" s="9" t="s">
+      <c r="A444" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="B444" s="10" t="s">
+      <c r="B444" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C444" s="10" t="s">
+      <c r="C444" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D444" s="10" t="s">
+      <c r="D444" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E444" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F444" s="10" t="s">
+      <c r="E444" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F444" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="445" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A445" s="9" t="s">
+      <c r="A445" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="B445" s="10" t="s">
+      <c r="B445" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C445" s="10" t="s">
+      <c r="C445" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D445" s="10" t="s">
+      <c r="D445" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E445" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F445" s="10" t="s">
+      <c r="E445" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F445" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="446" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A446" s="9" t="s">
+      <c r="A446" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="B446" s="10" t="s">
+      <c r="B446" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C446" s="10" t="s">
+      <c r="C446" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D446" s="10" t="s">
+      <c r="D446" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E446" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F446" s="10" t="s">
+      <c r="E446" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F446" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="447" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A447" s="9" t="s">
+      <c r="A447" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="B447" s="10" t="s">
+      <c r="B447" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C447" s="10" t="s">
+      <c r="C447" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D447" s="10" t="s">
+      <c r="D447" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E447" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F447" s="10" t="s">
+      <c r="E447" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F447" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11712,42 +11706,42 @@
       </c>
     </row>
     <row r="449" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A449" s="9" t="s">
+      <c r="A449" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B449" s="10" t="s">
+      <c r="B449" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C449" s="10" t="s">
+      <c r="C449" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D449" s="10" t="s">
+      <c r="D449" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E449" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F449" s="10" t="s">
+      <c r="E449" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F449" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="450" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A450" s="9" t="s">
+      <c r="A450" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B450" s="10" t="s">
+      <c r="B450" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C450" s="10" t="s">
+      <c r="C450" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D450" s="10" t="s">
+      <c r="D450" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E450" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F450" s="10" t="s">
+      <c r="E450" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F450" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11852,42 +11846,42 @@
       </c>
     </row>
     <row r="456" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A456" s="9" t="s">
+      <c r="A456" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="B456" s="10" t="s">
+      <c r="B456" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C456" s="10" t="s">
+      <c r="C456" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D456" s="10" t="s">
+      <c r="D456" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E456" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F456" s="10" t="s">
+      <c r="E456" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F456" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="457" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A457" s="9" t="s">
+      <c r="A457" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="B457" s="10" t="s">
+      <c r="B457" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C457" s="10" t="s">
+      <c r="C457" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D457" s="10" t="s">
+      <c r="D457" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E457" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F457" s="10" t="s">
+      <c r="E457" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F457" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11912,42 +11906,42 @@
       </c>
     </row>
     <row r="459" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A459" s="9" t="s">
+      <c r="A459" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="B459" s="10" t="s">
+      <c r="B459" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C459" s="10" t="s">
+      <c r="C459" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D459" s="10" t="s">
+      <c r="D459" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E459" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F459" s="10" t="s">
+      <c r="E459" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F459" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="460" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A460" s="9" t="s">
+      <c r="A460" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="B460" s="10" t="s">
+      <c r="B460" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C460" s="10" t="s">
+      <c r="C460" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D460" s="10" t="s">
+      <c r="D460" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E460" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F460" s="10" t="s">
+      <c r="E460" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F460" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11972,22 +11966,22 @@
       </c>
     </row>
     <row r="462" s="1" customFormat="1" ht="22" customHeight="1" spans="1:6">
-      <c r="A462" s="9" t="s">
+      <c r="A462" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="B462" s="10" t="s">
+      <c r="B462" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C462" s="10" t="s">
+      <c r="C462" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D462" s="10" t="s">
+      <c r="D462" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E462" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F462" s="10" t="s">
+      <c r="E462" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F462" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -13032,12 +13026,12 @@
       </c>
     </row>
     <row r="516" spans="1:1">
-      <c r="A516" s="13" t="s">
+      <c r="A516" s="11" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="517" spans="1:1">
-      <c r="A517" s="13" t="s">
+      <c r="A517" s="11" t="s">
         <v>571</v>
       </c>
     </row>
